--- a/weeks/undefined_20260928.xlsx
+++ b/weeks/undefined_20260928.xlsx
@@ -359,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
@@ -487,28 +487,22 @@
     <xf numFmtId="164" fontId="25" fillId="8" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="19" fillId="7" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="25" fillId="8" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="6" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="6" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="24" fillId="8" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="30" fillId="6" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="6" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="29" fillId="6" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="17" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
@@ -619,13 +613,13 @@
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14" t="n">
-        <v>7.25</v>
+        <v>0.0</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>4.66</v>
+        <v>0.0</v>
       </c>
       <c r="G3" s="16" t="inlineStr">
         <is>
@@ -633,13 +627,13 @@
         </is>
       </c>
       <c r="H3" s="37" t="n">
-        <v>4.66</v>
+        <v>0.0</v>
       </c>
       <c r="I3" s="18" t="n">
         <v>0.0</v>
       </c>
       <c r="J3" s="38" t="n">
-        <v>4.66</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4" customHeight="true" ht="21.75">
@@ -655,13 +649,13 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="21" t="n">
-        <v>7.25</v>
+        <v>0.0</v>
       </c>
       <c r="E4" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>4.66</v>
+        <v>0.0</v>
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
@@ -669,13 +663,13 @@
         </is>
       </c>
       <c r="H4" s="39" t="n">
-        <v>4.66</v>
+        <v>0.0</v>
       </c>
       <c r="I4" s="25" t="n">
         <v>0.0</v>
       </c>
       <c r="J4" s="40" t="n">
-        <v>4.66</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5" customHeight="true" ht="21.75">
@@ -691,27 +685,27 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>7.25</v>
+        <v>0.0</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>7.25</v>
+        <v>0.0</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>4.66</v>
+        <v>0.0</v>
       </c>
       <c r="G5" s="29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="41" t="n">
-        <v>4.66</v>
+      <c r="H5" s="30" t="n">
+        <v>0.0</v>
       </c>
       <c r="I5" s="31" t="n">
         <v>0.0</v>
       </c>
-      <c r="J5" s="42" t="n">
-        <v>4.66</v>
+      <c r="J5" s="31" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" customHeight="true" ht="21.75">
@@ -749,27 +743,27 @@
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
       <c r="D7" s="14" t="n">
-        <v>18.82</v>
+        <v>12.1</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>17.97</v>
+        <v>29.56</v>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="H7" s="37" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="I7" s="43" t="n">
-        <v>19.2</v>
+        <v>0.96</v>
+      </c>
+      <c r="I7" s="38" t="n">
+        <v>30.21</v>
       </c>
       <c r="J7" s="38" t="n">
-        <v>-1.23</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="8" customHeight="true" ht="21.75">
@@ -785,27 +779,27 @@
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="21" t="n">
-        <v>6.36</v>
+        <v>5.6</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>6.84</v>
+        <v>8.85</v>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H8" s="39" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="I8" s="44" t="n">
-        <v>8.1</v>
+        <v>-0.15</v>
+      </c>
+      <c r="I8" s="40" t="n">
+        <v>8.91</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>-1.26</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="9" customHeight="true" ht="21.75">
@@ -821,27 +815,27 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>6.36</v>
+        <v>5.6</v>
       </c>
       <c r="E9" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>6.84</v>
+        <v>8.85</v>
       </c>
       <c r="G9" s="29" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H9" s="41" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="I9" s="45" t="n">
-        <v>8.1</v>
+        <v>-0.15</v>
+      </c>
+      <c r="I9" s="42" t="n">
+        <v>8.91</v>
       </c>
       <c r="J9" s="42" t="n">
-        <v>-1.26</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="10" customHeight="true" ht="21.75">
@@ -857,27 +851,27 @@
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="21" t="n">
-        <v>8.59</v>
+        <v>5.25</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>8.3</v>
+        <v>8.05</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="H10" s="39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I10" s="44" t="n">
-        <v>8.1</v>
+        <v>-0.55</v>
+      </c>
+      <c r="I10" s="43" t="n">
+        <v>9.1</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>0.2</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="11" customHeight="true" ht="21.75">
@@ -893,27 +887,27 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>8.59</v>
+        <v>5.25</v>
       </c>
       <c r="E11" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F11" s="28" t="n">
-        <v>8.3</v>
+        <v>8.05</v>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="H11" s="46" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I11" s="45" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J11" s="45" t="n">
-        <v>0.2</v>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="H11" s="41" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="I11" s="44" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J11" s="42" t="n">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="12" customHeight="true" ht="21.75">
@@ -929,27 +923,27 @@
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21" t="n">
-        <v>3.87</v>
+        <v>0.48</v>
       </c>
       <c r="E12" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>2.83</v>
+        <v>11.58</v>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H12" s="39" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="I12" s="25" t="n">
-        <v>3.0</v>
+        <v>1.78</v>
+      </c>
+      <c r="I12" s="40" t="n">
+        <v>11.88</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>-0.17</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="13" customHeight="true" ht="21.75">
@@ -965,27 +959,27 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>3.87</v>
+        <v>0.48</v>
       </c>
       <c r="E13" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F13" s="28" t="n">
-        <v>2.83</v>
+        <v>11.58</v>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H13" s="41" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="I13" s="31" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>-0.17</v>
+        <v>1.78</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="J13" s="44" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="14" customHeight="true" ht="21.75">
@@ -1001,27 +995,27 @@
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" t="n">
-        <v>0.0</v>
+        <v>0.77</v>
       </c>
       <c r="E14" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.0</v>
+        <v>1.08</v>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="H14" s="39" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="I14" s="25" t="n">
-        <v>0.0</v>
+        <v>-0.12</v>
+      </c>
+      <c r="I14" s="40" t="n">
+        <v>0.32</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>0.0</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="15" customHeight="true" ht="21.75">
@@ -1037,27 +1031,27 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>0.0</v>
+        <v>0.77</v>
       </c>
       <c r="E15" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F15" s="28" t="n">
-        <v>0.0</v>
+        <v>1.08</v>
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H15" s="46" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="I15" s="31" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="31" t="n">
-        <v>0.0</v>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="H15" s="41" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I15" s="42" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J15" s="42" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="16" customHeight="true" ht="21.75">
@@ -1069,27 +1063,27 @@
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="14" t="n">
-        <v>6.85</v>
+        <v>10.09</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>5.32</v>
+        <v>7.26</v>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H16" s="37" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="I16" s="43" t="n">
-        <v>5.4</v>
+        <v>0.76</v>
+      </c>
+      <c r="I16" s="38" t="n">
+        <v>6.39</v>
       </c>
       <c r="J16" s="38" t="n">
-        <v>-0.08</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="17" customHeight="true" ht="21.75">
@@ -1105,27 +1099,27 @@
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H17" s="39" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I17" s="44" t="n">
-        <v>1.4</v>
+        <v>0.29</v>
+      </c>
+      <c r="I17" s="43" t="n">
+        <v>1.5</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="18" customHeight="true" ht="21.75">
@@ -1141,27 +1135,27 @@
         </is>
       </c>
       <c r="D18" s="32" t="n">
-        <v>1.56</v>
+        <v>2.31</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F18" s="33" t="n">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="G18" s="34" t="inlineStr">
         <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="H18" s="47" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I18" s="48" t="n">
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H18" s="45" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I18" s="46" t="n">
         <v>1.2</v>
       </c>
-      <c r="J18" s="49" t="n">
-        <v>0.36</v>
+      <c r="J18" s="47" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="19" customHeight="true" ht="21.75">
@@ -1177,27 +1171,27 @@
         </is>
       </c>
       <c r="D19" s="27" t="n">
-        <v>0.87</v>
+        <v>0.0</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H19" s="41" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I19" s="45" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
+      </c>
+      <c r="I19" s="44" t="n">
+        <v>0.3</v>
       </c>
       <c r="J19" s="42" t="n">
-        <v>0.37</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="20" customHeight="true" ht="21.75">
@@ -1213,27 +1207,27 @@
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" t="n">
-        <v>2.94</v>
+        <v>6.22</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>2.24</v>
+        <v>3.85</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="H20" s="39" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="I20" s="44" t="n">
-        <v>3.1</v>
+        <v>0.35</v>
+      </c>
+      <c r="I20" s="40" t="n">
+        <v>3.74</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>-0.86</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="21" customHeight="true" ht="21.75">
@@ -1249,13 +1243,13 @@
         </is>
       </c>
       <c r="D21" s="27" t="n">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
@@ -1263,13 +1257,13 @@
         </is>
       </c>
       <c r="H21" s="41" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="I21" s="45" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J21" s="42" t="n">
-        <v>-0.59</v>
+        <v>0.34</v>
+      </c>
+      <c r="I21" s="42" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J21" s="44" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="22" customHeight="true" ht="21.75">
@@ -1285,27 +1279,27 @@
         </is>
       </c>
       <c r="D22" s="32" t="n">
-        <v>1.21</v>
+        <v>3.32</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F22" s="33" t="n">
-        <v>1.13</v>
+        <v>1.51</v>
       </c>
       <c r="G22" s="34" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H22" s="47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I22" s="48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J22" s="49" t="n">
-        <v>-0.27</v>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="H22" s="45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I22" s="46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J22" s="47" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="23" customHeight="true" ht="21.75">
@@ -1321,27 +1315,27 @@
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>0.95</v>
+        <v>1.32</v>
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="H23" s="39" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="I23" s="44" t="n">
-        <v>0.9</v>
+        <v>0.12</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>1.15</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="24" customHeight="true" ht="21.75">
@@ -1357,27 +1351,27 @@
         </is>
       </c>
       <c r="D24" s="32" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>0.95</v>
+        <v>1.32</v>
       </c>
       <c r="G24" s="34" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="H24" s="47" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="I24" s="48" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J24" s="49" t="n">
-        <v>0.05</v>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="H24" s="45" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I24" s="47" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J24" s="47" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="25" customHeight="true" ht="21.75">
@@ -1389,27 +1383,27 @@
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="14" t="n">
-        <v>8.76</v>
+        <v>7.86</v>
       </c>
       <c r="E25" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>7.84</v>
+        <v>7.27</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="H25" s="37" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I25" s="43" t="n">
-        <v>7.7</v>
+        <v>-0.63</v>
+      </c>
+      <c r="I25" s="38" t="n">
+        <v>8.43</v>
       </c>
       <c r="J25" s="38" t="n">
-        <v>0.14</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="26" customHeight="true" ht="21.75">
@@ -1425,27 +1419,27 @@
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" t="n">
-        <v>6.95</v>
+        <v>5.16</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>6.02</v>
+        <v>5.51</v>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="H26" s="39" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I26" s="44" t="n">
-        <v>5.8</v>
+        <v>-0.59</v>
+      </c>
+      <c r="I26" s="40" t="n">
+        <v>6.71</v>
       </c>
       <c r="J26" s="40" t="n">
-        <v>0.22</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="27" customHeight="true" ht="21.75">
@@ -1461,27 +1455,27 @@
         </is>
       </c>
       <c r="D27" s="27" t="n">
-        <v>6.95</v>
+        <v>5.16</v>
       </c>
       <c r="E27" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>6.02</v>
+        <v>5.51</v>
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="H27" s="41" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I27" s="45" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J27" s="42" t="n">
-        <v>0.22</v>
+        <v>-0.59</v>
+      </c>
+      <c r="I27" s="42" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="J27" s="44" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="28" customHeight="true" ht="21.75">
@@ -1497,27 +1491,27 @@
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="E28" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H28" s="39" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I28" s="44" t="n">
-        <v>1.9</v>
+        <v>-0.04</v>
+      </c>
+      <c r="I28" s="40" t="n">
+        <v>1.72</v>
       </c>
       <c r="J28" s="40" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="29" customHeight="true" ht="21.75">
@@ -1533,27 +1527,27 @@
         </is>
       </c>
       <c r="D29" s="27" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="E29" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F29" s="28" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H29" s="41" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I29" s="45" t="n">
-        <v>1.9</v>
+        <v>-0.04</v>
+      </c>
+      <c r="I29" s="42" t="n">
+        <v>1.72</v>
       </c>
       <c r="J29" s="42" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="30" customHeight="true" ht="21.75">
@@ -1565,27 +1559,27 @@
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="14" t="n">
-        <v>14.92</v>
+        <v>16.2</v>
       </c>
       <c r="E30" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>14.03</v>
+        <v>14.26</v>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H30" s="37" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="I30" s="43" t="n">
-        <v>17.2</v>
+        <v>-1.74</v>
+      </c>
+      <c r="I30" s="38" t="n">
+        <v>15.82</v>
       </c>
       <c r="J30" s="38" t="n">
-        <v>-3.17</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="31" customHeight="true" ht="21.75">
@@ -1601,27 +1595,27 @@
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" t="n">
-        <v>5.34</v>
+        <v>5.26</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>4.54</v>
+        <v>2.82</v>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="H31" s="39" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I31" s="44" t="n">
-        <v>3.3</v>
+        <v>-0.28</v>
+      </c>
+      <c r="I31" s="40" t="n">
+        <v>2.97</v>
       </c>
       <c r="J31" s="40" t="n">
-        <v>1.24</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="32" customHeight="true" ht="21.75">
@@ -1637,27 +1631,27 @@
         </is>
       </c>
       <c r="D32" s="32" t="n">
-        <v>5.34</v>
+        <v>5.26</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F32" s="33" t="n">
-        <v>4.54</v>
+        <v>2.82</v>
       </c>
       <c r="G32" s="34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H32" s="47" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I32" s="48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J32" s="49" t="n">
-        <v>1.24</v>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="H32" s="45" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="I32" s="47" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J32" s="47" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="33" customHeight="true" ht="21.75">
@@ -1673,27 +1667,27 @@
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" t="n">
-        <v>6.34</v>
+        <v>7.29</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>6.7</v>
+        <v>3.98</v>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="H33" s="39" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="I33" s="44" t="n">
-        <v>8.1</v>
+        <v>-0.92</v>
+      </c>
+      <c r="I33" s="40" t="n">
+        <v>4.78</v>
       </c>
       <c r="J33" s="40" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="34" customHeight="true" ht="21.75">
@@ -1709,27 +1703,27 @@
         </is>
       </c>
       <c r="D34" s="32" t="n">
-        <v>6.34</v>
+        <v>7.29</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F34" s="33" t="n">
-        <v>6.7</v>
+        <v>3.98</v>
       </c>
       <c r="G34" s="34" t="inlineStr">
         <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="H34" s="50" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="I34" s="48" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J34" s="48" t="n">
-        <v>-1.4</v>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="H34" s="45" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="I34" s="47" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="J34" s="46" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="35" customHeight="true" ht="21.75">
@@ -1745,27 +1739,27 @@
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" t="n">
-        <v>3.24</v>
+        <v>3.65</v>
       </c>
       <c r="E35" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>2.79</v>
+        <v>7.46</v>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H35" s="39" t="n">
-        <v>-2.81</v>
-      </c>
-      <c r="I35" s="44" t="n">
-        <v>5.8</v>
+        <v>-0.54</v>
+      </c>
+      <c r="I35" s="40" t="n">
+        <v>8.07</v>
       </c>
       <c r="J35" s="40" t="n">
-        <v>-3.01</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="36" customHeight="true" ht="21.75">
@@ -1781,27 +1775,27 @@
         </is>
       </c>
       <c r="D36" s="32" t="n">
-        <v>3.24</v>
+        <v>3.65</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F36" s="33" t="n">
-        <v>2.79</v>
+        <v>7.46</v>
       </c>
       <c r="G36" s="34" t="inlineStr">
         <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="H36" s="47" t="n">
-        <v>-2.81</v>
-      </c>
-      <c r="I36" s="48" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J36" s="49" t="n">
-        <v>-3.01</v>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H36" s="45" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="I36" s="47" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="J36" s="47" t="n">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="37" customHeight="true" ht="21.75">
@@ -1813,27 +1807,27 @@
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="14" t="n">
-        <v>10.74</v>
+        <v>20.76</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>12.97</v>
+        <v>15.17</v>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H37" s="37" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="I37" s="43" t="n">
-        <v>14.2</v>
+        <v>0.17</v>
+      </c>
+      <c r="I37" s="38" t="n">
+        <v>14.89</v>
       </c>
       <c r="J37" s="38" t="n">
-        <v>-1.23</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="38" customHeight="true" ht="21.75">
@@ -1849,27 +1843,27 @@
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" t="n">
-        <v>0.81</v>
+        <v>5.89</v>
       </c>
       <c r="E38" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>3.19</v>
+        <v>4.15</v>
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="H38" s="39" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="I38" s="44" t="n">
-        <v>3.2</v>
+        <v>-0.15</v>
+      </c>
+      <c r="I38" s="40" t="n">
+        <v>3.66</v>
       </c>
       <c r="J38" s="40" t="n">
-        <v>-0.01</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="39" customHeight="true" ht="21.75">
@@ -1885,27 +1879,27 @@
         </is>
       </c>
       <c r="D39" s="27" t="n">
-        <v>0.81</v>
+        <v>5.89</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>3.19</v>
+        <v>4.15</v>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="H39" s="41" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="I39" s="45" t="n">
-        <v>3.2</v>
+        <v>-0.15</v>
+      </c>
+      <c r="I39" s="42" t="n">
+        <v>3.66</v>
       </c>
       <c r="J39" s="42" t="n">
-        <v>-0.01</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="40" customHeight="true" ht="21.75">
@@ -1921,27 +1915,27 @@
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="21" t="n">
-        <v>5.32</v>
+        <v>7.54</v>
       </c>
       <c r="E40" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>5.32</v>
+        <v>5.52</v>
       </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="H40" s="39" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I40" s="44" t="n">
-        <v>5.3</v>
+        <v>-0.28</v>
+      </c>
+      <c r="I40" s="40" t="n">
+        <v>6.57</v>
       </c>
       <c r="J40" s="40" t="n">
-        <v>0.02</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="41" customHeight="true" ht="21.75">
@@ -1957,27 +1951,27 @@
         </is>
       </c>
       <c r="D41" s="27" t="n">
-        <v>5.32</v>
+        <v>7.54</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>5.32</v>
+        <v>5.52</v>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="H41" s="41" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I41" s="45" t="n">
-        <v>5.3</v>
+        <v>-0.28</v>
+      </c>
+      <c r="I41" s="42" t="n">
+        <v>6.57</v>
       </c>
       <c r="J41" s="42" t="n">
-        <v>0.02</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="42" customHeight="true" ht="21.75">
@@ -1993,27 +1987,27 @@
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="21" t="n">
-        <v>4.61</v>
+        <v>7.33</v>
       </c>
       <c r="E42" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>4.46</v>
+        <v>5.5</v>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="H42" s="39" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="I42" s="44" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
+      </c>
+      <c r="I42" s="40" t="n">
+        <v>4.66</v>
       </c>
       <c r="J42" s="40" t="n">
-        <v>-1.24</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="43" customHeight="true" ht="21.75">
@@ -2029,27 +2023,27 @@
         </is>
       </c>
       <c r="D43" s="27" t="n">
-        <v>4.61</v>
+        <v>7.33</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>4.46</v>
+        <v>5.5</v>
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="H43" s="41" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="I43" s="45" t="n">
-        <v>5.7</v>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="H43" s="48" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I43" s="42" t="n">
+        <v>4.66</v>
       </c>
       <c r="J43" s="42" t="n">
-        <v>-1.24</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="44" customHeight="true" ht="21.75">
@@ -2061,27 +2055,27 @@
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
       <c r="D44" s="14" t="n">
-        <v>12.4</v>
+        <v>16.65</v>
       </c>
       <c r="E44" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>17.28</v>
+        <v>13.29</v>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="H44" s="37" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I44" s="43" t="n">
-        <v>14.9</v>
+        <v>1.49</v>
+      </c>
+      <c r="I44" s="38" t="n">
+        <v>10.81</v>
       </c>
       <c r="J44" s="38" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="45" customHeight="true" ht="21.75">
@@ -2097,27 +2091,27 @@
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="21" t="n">
-        <v>4.42</v>
+        <v>5.31</v>
       </c>
       <c r="E45" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>6.53</v>
+        <v>5.09</v>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="H45" s="39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I45" s="44" t="n">
-        <v>5.1</v>
+        <v>-0.11</v>
+      </c>
+      <c r="I45" s="40" t="n">
+        <v>4.41</v>
       </c>
       <c r="J45" s="40" t="n">
-        <v>1.43</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="46" customHeight="true" ht="21.75">
@@ -2133,27 +2127,27 @@
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>4.42</v>
+        <v>5.31</v>
       </c>
       <c r="E46" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F46" s="33" t="n">
-        <v>6.53</v>
+        <v>5.09</v>
       </c>
       <c r="G46" s="34" t="inlineStr">
         <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="H46" s="47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I46" s="48" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J46" s="49" t="n">
-        <v>1.43</v>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="H46" s="45" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I46" s="47" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="J46" s="47" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="47" customHeight="true" ht="21.75">
@@ -2169,27 +2163,27 @@
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="21" t="n">
-        <v>4.73</v>
+        <v>9.62</v>
       </c>
       <c r="E47" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F47" s="22" t="n">
-        <v>7.13</v>
+        <v>6.25</v>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="H47" s="39" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="I47" s="44" t="n">
-        <v>4.9</v>
+        <v>1.45</v>
+      </c>
+      <c r="I47" s="40" t="n">
+        <v>4.56</v>
       </c>
       <c r="J47" s="40" t="n">
-        <v>2.23</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="48" customHeight="true" ht="21.75">
@@ -2205,27 +2199,27 @@
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>1.32</v>
+        <v>4.74</v>
       </c>
       <c r="E48" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F48" s="33" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="G48" s="34" t="inlineStr">
         <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="H48" s="50" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="I48" s="48" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J48" s="48" t="n">
-        <v>-1.5</v>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="H48" s="45" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="I48" s="47" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="J48" s="47" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="49" customHeight="true" ht="21.75">
@@ -2241,13 +2235,13 @@
         </is>
       </c>
       <c r="D49" s="27" t="n">
-        <v>3.41</v>
+        <v>4.88</v>
       </c>
       <c r="E49" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>3.73</v>
+        <v>2.57</v>
       </c>
       <c r="G49" s="29" t="inlineStr">
         <is>
@@ -2255,13 +2249,13 @@
         </is>
       </c>
       <c r="H49" s="41" t="n">
-        <v>3.73</v>
+        <v>2.57</v>
       </c>
       <c r="I49" s="31" t="n">
         <v>0.0</v>
       </c>
       <c r="J49" s="42" t="n">
-        <v>3.73</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="50" customHeight="true" ht="21.75">
@@ -2277,27 +2271,27 @@
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="21" t="n">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="E50" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H50" s="39" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="I50" s="44" t="n">
-        <v>4.9</v>
+        <v>0.15</v>
+      </c>
+      <c r="I50" s="40" t="n">
+        <v>1.84</v>
       </c>
       <c r="J50" s="40" t="n">
-        <v>-1.28</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="51" customHeight="true" ht="21.75">
@@ -2313,27 +2307,27 @@
         </is>
       </c>
       <c r="D51" s="27" t="n">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="E51" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F51" s="28" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="G51" s="29" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H51" s="41" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="I51" s="45" t="n">
-        <v>4.9</v>
+        <v>0.15</v>
+      </c>
+      <c r="I51" s="42" t="n">
+        <v>1.84</v>
       </c>
       <c r="J51" s="42" t="n">
-        <v>-1.28</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="52" customHeight="true" ht="21.75">
@@ -2345,27 +2339,27 @@
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
       <c r="D52" s="14" t="n">
-        <v>18.21</v>
+        <v>14.99</v>
       </c>
       <c r="E52" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>16.91</v>
+        <v>11.32</v>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="H52" s="37" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="I52" s="43" t="n">
-        <v>20.3</v>
+        <v>-1.48</v>
+      </c>
+      <c r="I52" s="38" t="n">
+        <v>12.58</v>
       </c>
       <c r="J52" s="38" t="n">
-        <v>-3.39</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="53" customHeight="true" ht="21.75">
@@ -2381,27 +2375,27 @@
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="21" t="n">
-        <v>3.0</v>
+        <v>3.13</v>
       </c>
       <c r="E53" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F53" s="22" t="n">
-        <v>3.07</v>
+        <v>2.57</v>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="H53" s="39" t="n">
-        <v>-1.33</v>
-      </c>
-      <c r="I53" s="44" t="n">
-        <v>4.7</v>
+        <v>-0.13</v>
+      </c>
+      <c r="I53" s="40" t="n">
+        <v>2.32</v>
       </c>
       <c r="J53" s="40" t="n">
-        <v>-1.63</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="54" customHeight="true" ht="21.75">
@@ -2417,27 +2411,27 @@
         </is>
       </c>
       <c r="D54" s="32" t="n">
-        <v>3.0</v>
+        <v>3.13</v>
       </c>
       <c r="E54" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F54" s="33" t="n">
-        <v>3.07</v>
+        <v>2.57</v>
       </c>
       <c r="G54" s="34" t="inlineStr">
         <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="H54" s="47" t="n">
-        <v>-1.33</v>
-      </c>
-      <c r="I54" s="48" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J54" s="49" t="n">
-        <v>-1.63</v>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="H54" s="45" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="I54" s="47" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J54" s="47" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="55" customHeight="true" ht="21.75">
@@ -2453,27 +2447,27 @@
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="21" t="n">
-        <v>9.14</v>
+        <v>5.91</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>7.57</v>
+        <v>5.08</v>
       </c>
       <c r="G55" s="23" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H55" s="39" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I55" s="44" t="n">
-        <v>7.7</v>
+        <v>-0.92</v>
+      </c>
+      <c r="I55" s="40" t="n">
+        <v>5.82</v>
       </c>
       <c r="J55" s="40" t="n">
-        <v>-0.13</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="56" customHeight="true" ht="21.75">
@@ -2489,27 +2483,27 @@
         </is>
       </c>
       <c r="D56" s="32" t="n">
-        <v>7.95</v>
+        <v>5.24</v>
       </c>
       <c r="E56" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F56" s="33" t="n">
-        <v>6.81</v>
+        <v>4.54</v>
       </c>
       <c r="G56" s="34" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="H56" s="47" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="I56" s="48" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J56" s="49" t="n">
-        <v>-0.89</v>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H56" s="45" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="I56" s="47" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="J56" s="47" t="n">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="57" customHeight="true" ht="21.75">
@@ -2525,13 +2519,13 @@
         </is>
       </c>
       <c r="D57" s="27" t="n">
-        <v>1.19</v>
+        <v>0.67</v>
       </c>
       <c r="E57" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F57" s="28" t="n">
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="G57" s="29" t="inlineStr">
         <is>
@@ -2539,13 +2533,13 @@
         </is>
       </c>
       <c r="H57" s="41" t="n">
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="I57" s="31" t="n">
         <v>0.0</v>
       </c>
       <c r="J57" s="42" t="n">
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="58" customHeight="true" ht="21.75">
@@ -2561,24 +2555,24 @@
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="21" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="E58" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F58" s="22" t="n">
-        <v>3.46</v>
+        <v>2.02</v>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="H58" s="39" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="I58" s="44" t="n">
-        <v>4.3</v>
+        <v>-0.48</v>
+      </c>
+      <c r="I58" s="40" t="n">
+        <v>2.86</v>
       </c>
       <c r="J58" s="40" t="n">
         <v>-0.84</v>
@@ -2597,24 +2591,24 @@
         </is>
       </c>
       <c r="D59" s="27" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>3.46</v>
+        <v>2.02</v>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="H59" s="41" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="I59" s="45" t="n">
-        <v>4.3</v>
+        <v>-0.48</v>
+      </c>
+      <c r="I59" s="42" t="n">
+        <v>2.86</v>
       </c>
       <c r="J59" s="42" t="n">
         <v>-0.84</v>
@@ -2633,27 +2627,27 @@
       </c>
       <c r="C60" s="20"/>
       <c r="D60" s="21" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="E60" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>2.81</v>
+        <v>1.65</v>
       </c>
       <c r="G60" s="23" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H60" s="39" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="I60" s="44" t="n">
-        <v>3.6</v>
+        <v>0.05</v>
+      </c>
+      <c r="I60" s="40" t="n">
+        <v>1.58</v>
       </c>
       <c r="J60" s="40" t="n">
-        <v>-0.79</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="61" customHeight="true" ht="21.75">
@@ -2669,27 +2663,27 @@
         </is>
       </c>
       <c r="D61" s="27" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>2.81</v>
+        <v>1.65</v>
       </c>
       <c r="G61" s="29" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H61" s="41" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="I61" s="45" t="n">
-        <v>3.6</v>
+        <v>0.05</v>
+      </c>
+      <c r="I61" s="42" t="n">
+        <v>1.58</v>
       </c>
       <c r="J61" s="42" t="n">
-        <v>-0.79</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="62" customHeight="true" ht="21.75">
@@ -2701,13 +2695,13 @@
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
       <c r="D62" s="14" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="E62" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
@@ -2715,13 +2709,13 @@
         </is>
       </c>
       <c r="H62" s="37" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I62" s="18" t="n">
-        <v>1.0</v>
+        <v>0.11</v>
+      </c>
+      <c r="I62" s="38" t="n">
+        <v>0.79</v>
       </c>
       <c r="J62" s="38" t="n">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="63" customHeight="true" ht="21.75">
@@ -2737,13 +2731,13 @@
       </c>
       <c r="C63" s="20"/>
       <c r="D63" s="21" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="E63" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F63" s="22" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="G63" s="23" t="inlineStr">
         <is>
@@ -2751,13 +2745,13 @@
         </is>
       </c>
       <c r="H63" s="39" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I63" s="25" t="n">
-        <v>1.0</v>
+        <v>0.11</v>
+      </c>
+      <c r="I63" s="40" t="n">
+        <v>0.79</v>
       </c>
       <c r="J63" s="40" t="n">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="64" customHeight="true" ht="21.75">
@@ -2773,27 +2767,27 @@
         </is>
       </c>
       <c r="D64" s="32" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="E64" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F64" s="33" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="G64" s="34" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="H64" s="47" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I64" s="36" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="J64" s="49" t="n">
-        <v>0.64</v>
+      <c r="H64" s="45" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I64" s="47" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J64" s="47" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="65" customHeight="true" ht="21.75">
@@ -2805,27 +2799,27 @@
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
       <c r="D65" s="14" t="n">
-        <v>0.83</v>
+        <v>0.0</v>
       </c>
       <c r="E65" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>1.38</v>
+        <v>0.56</v>
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H65" s="37" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I65" s="43" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
+      </c>
+      <c r="I65" s="18" t="n">
+        <v>0.0</v>
       </c>
       <c r="J65" s="38" t="n">
-        <v>1.18</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="66" customHeight="true" ht="21.75">
@@ -2841,27 +2835,27 @@
       </c>
       <c r="C66" s="20"/>
       <c r="D66" s="21" t="n">
-        <v>0.83</v>
+        <v>0.0</v>
       </c>
       <c r="E66" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>1.38</v>
+        <v>0.56</v>
       </c>
       <c r="G66" s="23" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H66" s="39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I66" s="44" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
+      </c>
+      <c r="I66" s="25" t="n">
+        <v>0.0</v>
       </c>
       <c r="J66" s="40" t="n">
-        <v>1.18</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="67" customHeight="true" ht="21.75">
@@ -2877,38 +2871,38 @@
         </is>
       </c>
       <c r="D67" s="27" t="n">
-        <v>0.83</v>
+        <v>0.0</v>
       </c>
       <c r="E67" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F67" s="28" t="n">
-        <v>1.38</v>
+        <v>0.56</v>
       </c>
       <c r="G67" s="29" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H67" s="41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I67" s="45" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
+      </c>
+      <c r="I67" s="31" t="n">
+        <v>0.0</v>
       </c>
       <c r="J67" s="42" t="n">
-        <v>1.18</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="10"/>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
-      <c r="D68" s="51" t="n">
+      <c r="D68" s="49" t="n">
         <v>100.0</v>
       </c>
       <c r="E68" s="10"/>
-      <c r="F68" s="51" t="n">
+      <c r="F68" s="49" t="n">
         <v>100.0</v>
       </c>
       <c r="G68" s="10" t="inlineStr">
@@ -2916,14 +2910,14 @@
           <t>100.00</t>
         </is>
       </c>
-      <c r="H68" s="52" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I68" s="51" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="J68" s="51" t="n">
-        <v>-0.1</v>
+      <c r="H68" s="50" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I68" s="49" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="J68" s="49" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
